--- a/research/traditional_assets/database/data/nigeria/nigeria_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.158</v>
+        <v>0.133</v>
       </c>
       <c r="E2">
-        <v>0.1855</v>
+        <v>0.136</v>
       </c>
       <c r="G2">
-        <v>0.1659110350727117</v>
+        <v>0.1275527629389614</v>
       </c>
       <c r="H2">
-        <v>0.1659110350727117</v>
+        <v>0.1275527629389614</v>
       </c>
       <c r="I2">
-        <v>0.1283297690333619</v>
+        <v>0.1446427007618881</v>
       </c>
       <c r="J2">
-        <v>0.1083204006293877</v>
+        <v>0.1142505635405622</v>
       </c>
       <c r="K2">
-        <v>46.488</v>
+        <v>51.267</v>
       </c>
       <c r="L2">
-        <v>0.09941830624465356</v>
+        <v>0.1122405639723268</v>
       </c>
       <c r="M2">
-        <v>6.687</v>
+        <v>15.7</v>
       </c>
       <c r="N2">
-        <v>0.02752758109665734</v>
+        <v>0.06821045314332884</v>
       </c>
       <c r="O2">
-        <v>0.1438435725348477</v>
+        <v>0.3062398814051924</v>
       </c>
       <c r="P2">
-        <v>6.673</v>
+        <v>15.7</v>
       </c>
       <c r="Q2">
-        <v>0.02746994895438828</v>
+        <v>0.06821045314332884</v>
       </c>
       <c r="R2">
-        <v>0.143542419549131</v>
+        <v>0.3062398814051924</v>
       </c>
       <c r="S2">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.002093614475848661</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>106.52</v>
+        <v>171.03</v>
       </c>
       <c r="V2">
-        <v>0.4384982710357319</v>
+        <v>0.7430594777772951</v>
       </c>
       <c r="W2">
-        <v>0.08791666666666666</v>
+        <v>0.0776268945173431</v>
       </c>
       <c r="X2">
-        <v>0.09315549302781131</v>
+        <v>0.1590710607568138</v>
       </c>
       <c r="Y2">
-        <v>-0.005238826361144658</v>
+        <v>-0.08144416623947072</v>
       </c>
       <c r="Z2">
-        <v>3.098802494416721</v>
+        <v>1.518786992086187</v>
       </c>
       <c r="AA2">
-        <v>0.1903882776358415</v>
+        <v>0.1219508217690451</v>
       </c>
       <c r="AB2">
-        <v>0.09261148688963715</v>
+        <v>0.1578958424186642</v>
       </c>
       <c r="AC2">
-        <v>0.09474796662501464</v>
+        <v>-0.03681792659354859</v>
       </c>
       <c r="AD2">
-        <v>19.533</v>
+        <v>20.209</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>19.533</v>
+        <v>20.209</v>
       </c>
       <c r="AG2">
-        <v>-86.98699999999999</v>
+        <v>-150.821</v>
       </c>
       <c r="AH2">
-        <v>0.07442475414645672</v>
+        <v>0.08071363812460311</v>
       </c>
       <c r="AI2">
-        <v>0.04585932529294513</v>
+        <v>0.03937004806071976</v>
       </c>
       <c r="AJ2">
-        <v>-0.557848563164949</v>
+        <v>-1.900729687834755</v>
       </c>
       <c r="AK2">
-        <v>-0.2723339375667239</v>
+        <v>-0.4406376085006676</v>
       </c>
       <c r="AL2">
-        <v>2.416</v>
+        <v>2.366</v>
       </c>
       <c r="AM2">
-        <v>2.416</v>
+        <v>2.366</v>
       </c>
       <c r="AN2">
-        <v>0.2874613686534216</v>
+        <v>0.2813761800005569</v>
       </c>
       <c r="AO2">
-        <v>24.8373344370861</v>
+        <v>27.92349957734573</v>
       </c>
       <c r="AP2">
-        <v>-1.280161883738043</v>
+        <v>-2.099927598785887</v>
       </c>
       <c r="AQ2">
-        <v>24.8373344370861</v>
+        <v>27.92349957734573</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Custodian Investment Plc (NGSE:CUSTODIAN)</t>
+          <t>Veritas Kapital Assurance Plc (NGSE:VERITASKAP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,104 +721,95 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.348</v>
-      </c>
-      <c r="E3">
-        <v>0.233</v>
-      </c>
       <c r="G3">
-        <v>0.1383104125736739</v>
+        <v>0.09179104477611939</v>
       </c>
       <c r="H3">
-        <v>0.1383104125736739</v>
+        <v>0.09179104477611939</v>
       </c>
       <c r="I3">
-        <v>0.1284872298624755</v>
+        <v>0.0676865671641791</v>
       </c>
       <c r="J3">
-        <v>0.1200765059021184</v>
+        <v>0.0676865671641791</v>
       </c>
       <c r="K3">
-        <v>29.9</v>
+        <v>1.43</v>
       </c>
       <c r="L3">
-        <v>0.1174852652259332</v>
+        <v>0.1067164179104478</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0001615508885298869</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.0006993006993006993</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0001615508885298869</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.0006993006993006993</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>33.1</v>
+        <v>9.49</v>
       </c>
       <c r="V3">
-        <v>0.2939609236234458</v>
+        <v>1.533117932148627</v>
       </c>
       <c r="X3">
-        <v>0.09551132032368022</v>
+        <v>0.1574845062704379</v>
       </c>
       <c r="AB3">
-        <v>0.09326898799712145</v>
+        <v>0.1574845062704379</v>
       </c>
       <c r="AD3">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-26.59</v>
+        <v>-9.49</v>
       </c>
       <c r="AH3">
-        <v>0.05465536059105029</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.04316689874676746</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.309150098825718</v>
+        <v>2.875757575757576</v>
       </c>
       <c r="AK3">
-        <v>-0.2258941466315521</v>
+        <v>-0.5612063867534005</v>
       </c>
       <c r="AL3">
-        <v>0.709</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.709</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.1849431818181818</v>
-      </c>
-      <c r="AO3">
-        <v>46.1212976022567</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.7553977272727274</v>
-      </c>
-      <c r="AQ3">
-        <v>46.1212976022567</v>
+        <v>-6.683098591549296</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Veritas Kapital Assurance Plc (NGSE:VERITASKAP)</t>
+          <t>Custodian Investment Plc (NGSE:CUSTODIAN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,92 +828,122 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.193</v>
+      </c>
+      <c r="E4">
+        <v>0.139</v>
+      </c>
       <c r="G4">
-        <v>0.1976377952755906</v>
+        <v>0.2038895859473024</v>
       </c>
       <c r="H4">
-        <v>0.1976377952755906</v>
+        <v>0.2038895859473024</v>
       </c>
       <c r="I4">
-        <v>0.1755905511811024</v>
+        <v>0.2151819322459222</v>
       </c>
       <c r="J4">
-        <v>0.1755905511811024</v>
+        <v>0.178772009273185</v>
       </c>
       <c r="K4">
-        <v>2.6</v>
+        <v>25.1</v>
       </c>
       <c r="L4">
-        <v>0.2047244094488189</v>
+        <v>0.157465495608532</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>6.81</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.08719590268886043</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.2713147410358566</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>6.81</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.08719590268886043</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.2713147410358566</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0</v>
+        <v>47.2</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.6043533930857875</v>
+      </c>
+      <c r="W4">
+        <v>0.2067545304777595</v>
       </c>
       <c r="X4">
-        <v>0.09238359951557647</v>
+        <v>0.1636755520904861</v>
+      </c>
+      <c r="Y4">
+        <v>0.0430789783872734</v>
+      </c>
+      <c r="Z4">
+        <v>1.681257251344795</v>
+      </c>
+      <c r="AA4">
+        <v>0.3005617369280212</v>
       </c>
       <c r="AB4">
-        <v>0.09238359951557647</v>
+        <v>0.1590395440547462</v>
+      </c>
+      <c r="AC4">
+        <v>0.1415221928732751</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>-41.38</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.06935176358436608</v>
+      </c>
+      <c r="AI4">
+        <v>0.03596588802373007</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>-1.126906318082789</v>
+      </c>
+      <c r="AK4">
+        <v>-0.3610190193683476</v>
       </c>
       <c r="AL4">
-        <v>0.003</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AM4">
-        <v>0.003</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>0.164872521246459</v>
       </c>
       <c r="AO4">
-        <v>743.3333333333333</v>
+        <v>50.14619883040935</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>-1.172237960339944</v>
       </c>
       <c r="AQ4">
-        <v>743.3333333333333</v>
+        <v>50.14619883040935</v>
       </c>
     </row>
     <row r="5">
@@ -933,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sunu Assurances Nigeria Plc (NGSE:SUNUASSUR)</t>
+          <t>NEM Insurance Plc (NGSE:NEM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -941,113 +962,116 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.00394</v>
-      </c>
       <c r="G5">
-        <v>0.105982905982906</v>
+        <v>0.1940035273368607</v>
       </c>
       <c r="H5">
-        <v>0.105982905982906</v>
+        <v>0.1940035273368607</v>
       </c>
       <c r="I5">
-        <v>0.05273504273504274</v>
+        <v>0.2645502645502645</v>
       </c>
       <c r="J5">
-        <v>0.02808714232627276</v>
+        <v>0.2502986857825568</v>
       </c>
       <c r="K5">
-        <v>0.368</v>
+        <v>14.6</v>
       </c>
       <c r="L5">
-        <v>0.03145299145299146</v>
+        <v>0.2574955908289241</v>
       </c>
       <c r="M5">
-        <v>0.118</v>
+        <v>2.31</v>
       </c>
       <c r="N5">
-        <v>0.01855345911949685</v>
+        <v>0.04583333333333334</v>
       </c>
       <c r="O5">
-        <v>0.3206521739130435</v>
+        <v>0.1582191780821918</v>
       </c>
       <c r="P5">
-        <v>0.104</v>
+        <v>2.31</v>
       </c>
       <c r="Q5">
-        <v>0.01635220125786164</v>
+        <v>0.04583333333333334</v>
       </c>
       <c r="R5">
-        <v>0.2826086956521739</v>
+        <v>0.1582191780821918</v>
       </c>
       <c r="S5">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.1186440677966102</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>8.32</v>
+        <v>19</v>
       </c>
       <c r="V5">
-        <v>1.308176100628931</v>
+        <v>0.376984126984127</v>
       </c>
       <c r="W5">
-        <v>0.03607843137254902</v>
+        <v>0.3022774327122154</v>
       </c>
       <c r="X5">
-        <v>0.09238359951557647</v>
+        <v>0.1576493458624802</v>
       </c>
       <c r="Y5">
-        <v>-0.05630516814302745</v>
+        <v>0.1446280868497352</v>
       </c>
       <c r="Z5">
-        <v>12.06185567010311</v>
+        <v>1.170858629661752</v>
       </c>
       <c r="AA5">
-        <v>0.338783056925146</v>
+        <v>0.2930643762415019</v>
       </c>
       <c r="AB5">
-        <v>0.09238359951557647</v>
+        <v>0.1575236398728533</v>
       </c>
       <c r="AC5">
-        <v>0.2463994574095696</v>
+        <v>0.1355407363686486</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG5">
-        <v>-8.32</v>
+        <v>-18.9</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.00198019801980198</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.001677852348993289</v>
       </c>
       <c r="AJ5">
-        <v>4.244897959183674</v>
+        <v>-0.6</v>
       </c>
       <c r="AK5">
-        <v>-0.8684759916492695</v>
+        <v>-0.4655172413793103</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>0.006410256410256411</v>
+      </c>
+      <c r="AO5">
+        <v>1666.666666666667</v>
       </c>
       <c r="AP5">
-        <v>-7.563636363636363</v>
+        <v>-1.211538461538461</v>
+      </c>
+      <c r="AQ5">
+        <v>1666.666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -1058,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AXA Mansard Insurance Plc (NGSE:MANSARD)</t>
+          <t>Sovereign Trust Insurance Plc (NGSE:SOVRENINS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1067,121 +1091,118 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.187</v>
+        <v>0.103</v>
       </c>
       <c r="E6">
-        <v>0.0983</v>
+        <v>0.106</v>
       </c>
       <c r="G6">
-        <v>0.2233104799216455</v>
+        <v>0.1351851851851852</v>
       </c>
       <c r="H6">
-        <v>0.2233104799216455</v>
+        <v>0.1351851851851852</v>
       </c>
       <c r="I6">
-        <v>0.1802154750244858</v>
+        <v>0.1226851851851852</v>
       </c>
       <c r="J6">
-        <v>0.1161034210777218</v>
+        <v>0.1054484236302418</v>
       </c>
       <c r="K6">
-        <v>8.67</v>
+        <v>2.08</v>
       </c>
       <c r="L6">
-        <v>0.08491674828599413</v>
+        <v>0.0962962962962963</v>
       </c>
       <c r="M6">
-        <v>4.82</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.09620758483033932</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.5559400230680508</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>4.82</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.09620758483033932</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.5559400230680508</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>22.5</v>
+        <v>12.1</v>
       </c>
       <c r="V6">
-        <v>0.4491017964071856</v>
+        <v>1.704225352112676</v>
       </c>
       <c r="W6">
-        <v>0.1124513618677043</v>
+        <v>0.09203539823008849</v>
       </c>
       <c r="X6">
-        <v>0.102058704029782</v>
+        <v>0.2056938183949369</v>
       </c>
       <c r="Y6">
-        <v>0.01039265783792231</v>
+        <v>-0.1136584201648484</v>
       </c>
       <c r="Z6">
-        <v>2.547405189620759</v>
+        <v>1.484536082474227</v>
       </c>
       <c r="AA6">
-        <v>0.2957624573861128</v>
+        <v>0.1565419897191218</v>
       </c>
       <c r="AB6">
-        <v>0.09484122482475965</v>
+        <v>0.1647413131497176</v>
       </c>
       <c r="AC6">
-        <v>0.2009212325613531</v>
+        <v>-0.00819932343059579</v>
       </c>
       <c r="AD6">
-        <v>8.960000000000001</v>
+        <v>4.12</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>8.960000000000001</v>
+        <v>4.12</v>
       </c>
       <c r="AG6">
-        <v>-13.54</v>
+        <v>-7.98</v>
       </c>
       <c r="AH6">
-        <v>0.1517101252963088</v>
+        <v>0.3672014260249555</v>
       </c>
       <c r="AI6">
-        <v>0.08927859705061778</v>
+        <v>0.1480948957584472</v>
       </c>
       <c r="AJ6">
-        <v>-0.3703501094091903</v>
+        <v>9.068181818181818</v>
       </c>
       <c r="AK6">
-        <v>-0.1739018751605445</v>
+        <v>-0.5076335877862596</v>
       </c>
       <c r="AL6">
-        <v>1.55</v>
+        <v>0.504</v>
       </c>
       <c r="AM6">
-        <v>1.55</v>
+        <v>0.504</v>
       </c>
       <c r="AN6">
-        <v>0.4186915887850468</v>
+        <v>1.350819672131148</v>
       </c>
       <c r="AO6">
-        <v>11.87096774193548</v>
+        <v>5.257936507936508</v>
       </c>
       <c r="AP6">
-        <v>-0.6327102803738318</v>
+        <v>-2.616393442622951</v>
       </c>
       <c r="AQ6">
-        <v>11.87096774193548</v>
+        <v>5.257936507936508</v>
       </c>
     </row>
     <row r="7">
@@ -1192,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sovereign Trust Insurance Plc (NGSE:SOVRENINS)</t>
+          <t>Consolidated Hallmark Insurance Plc (NGSE:CHIPLC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,118 +1222,115 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.196</v>
+        <v>0.143</v>
       </c>
       <c r="E7">
-        <v>0.269</v>
+        <v>0.349</v>
       </c>
       <c r="G7">
-        <v>0.1182222222222222</v>
+        <v>0.1009615384615385</v>
       </c>
       <c r="H7">
-        <v>0.1182222222222222</v>
+        <v>0.1009615384615385</v>
       </c>
       <c r="I7">
-        <v>0.1071111111111111</v>
+        <v>0.1129807692307692</v>
       </c>
       <c r="J7">
-        <v>0.0902863521055302</v>
+        <v>0.09281804733727811</v>
       </c>
       <c r="K7">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="L7">
-        <v>0.08222222222222222</v>
+        <v>0.1028846153846154</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>0.502</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.03098765432098766</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.2345794392523364</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>0.502</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.03098765432098766</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.2345794392523364</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>11.6</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="V7">
-        <v>1.404358353510896</v>
+        <v>0.6154320987654321</v>
       </c>
       <c r="W7">
-        <v>0.08564814814814814</v>
+        <v>0.1014218009478673</v>
       </c>
       <c r="X7">
-        <v>0.1156341739461101</v>
+        <v>0.1698950960001985</v>
       </c>
       <c r="Y7">
-        <v>-0.02998602579796192</v>
+        <v>-0.06847329505233121</v>
       </c>
       <c r="Z7">
-        <v>2.108716026241799</v>
+        <v>1.430634844212119</v>
       </c>
       <c r="AA7">
-        <v>0.1903882776358415</v>
+        <v>0.13278873269244</v>
       </c>
       <c r="AB7">
-        <v>0.0956403110108269</v>
+        <v>0.1600529904547495</v>
       </c>
       <c r="AC7">
-        <v>0.09474796662501464</v>
+        <v>-0.02726425776230956</v>
       </c>
       <c r="AD7">
-        <v>3.55</v>
+        <v>2.42</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3.55</v>
+        <v>2.42</v>
       </c>
       <c r="AG7">
-        <v>-8.050000000000001</v>
+        <v>-7.550000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.3005927180355631</v>
+        <v>0.129967776584318</v>
       </c>
       <c r="AI7">
-        <v>0.135755258126195</v>
+        <v>0.09950657894736842</v>
       </c>
       <c r="AJ7">
-        <v>-38.33333333333351</v>
+        <v>-0.8728323699421967</v>
       </c>
       <c r="AK7">
-        <v>-0.5532646048109966</v>
+        <v>-0.5261324041811848</v>
       </c>
       <c r="AL7">
-        <v>0.096</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>0.096</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>1.272401433691756</v>
-      </c>
-      <c r="AO7">
-        <v>25.10416666666667</v>
+        <v>0.8768115942028986</v>
       </c>
       <c r="AP7">
-        <v>-2.885304659498208</v>
-      </c>
-      <c r="AQ7">
-        <v>25.10416666666667</v>
+        <v>-2.735507246376812</v>
       </c>
     </row>
     <row r="8">
@@ -1323,7 +1341,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Regency Alliance Insurance Plc (NGSE:REGALINS)</t>
+          <t>Sunu Assurances Nigeria Plc (NGSE:SUNUASSUR)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1332,76 +1350,79 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0925</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="E8">
-        <v>0.00522</v>
+        <v>0.375</v>
       </c>
       <c r="G8">
-        <v>0.1193548387096774</v>
+        <v>0.1393162393162393</v>
       </c>
       <c r="H8">
-        <v>0.1193548387096774</v>
+        <v>0.1393162393162393</v>
       </c>
       <c r="I8">
-        <v>0.1225806451612903</v>
+        <v>0.1350427350427351</v>
       </c>
       <c r="J8">
-        <v>0.1128667072428484</v>
+        <v>0.0852815332815333</v>
       </c>
       <c r="K8">
-        <v>1.59</v>
+        <v>0.958</v>
       </c>
       <c r="L8">
-        <v>0.1282258064516129</v>
+        <v>0.08188034188034188</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.02659574468085107</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.104384133611691</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.02659574468085107</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.104384133611691</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>5.83</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V8">
-        <v>0.7075242718446602</v>
+        <v>2.473404255319149</v>
       </c>
       <c r="W8">
-        <v>0.09085714285714286</v>
+        <v>0.05537572254335259</v>
       </c>
       <c r="X8">
-        <v>0.09238359951557647</v>
+        <v>0.1574845062704379</v>
       </c>
       <c r="Y8">
-        <v>-0.001526456658433609</v>
+        <v>-0.1021087837270853</v>
       </c>
       <c r="Z8">
-        <v>1.293013555787278</v>
+        <v>1.302895322939866</v>
       </c>
       <c r="AA8">
-        <v>0.1459381824620773</v>
+        <v>0.1111129108456503</v>
       </c>
       <c r="AB8">
-        <v>0.09238359951557647</v>
+        <v>0.1574845062704379</v>
       </c>
       <c r="AC8">
-        <v>0.0535545829465008</v>
+        <v>-0.04637159542478761</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1413,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>-5.83</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -1422,28 +1443,22 @@
         <v>0</v>
       </c>
       <c r="AJ8">
-        <v>-2.41908713692946</v>
+        <v>1.67870036101083</v>
       </c>
       <c r="AK8">
-        <v>-0.456538762725137</v>
+        <v>-1.120481927710843</v>
       </c>
       <c r="AL8">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="AN8">
         <v>0</v>
       </c>
-      <c r="AO8">
-        <v>66.08695652173913</v>
-      </c>
       <c r="AP8">
-        <v>-3.275280898876404</v>
-      </c>
-      <c r="AQ8">
-        <v>66.08695652173913</v>
+        <v>-4.492753623188406</v>
       </c>
     </row>
     <row r="9">
@@ -1454,7 +1469,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Consolidated Hallmark Insurance Plc (NGSE:CHIPLC)</t>
+          <t>Regency Alliance Insurance Plc (NGSE:REGALINS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1463,115 +1478,118 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.112</v>
+        <v>-0.182</v>
       </c>
       <c r="E9">
-        <v>0.138</v>
+        <v>-0.0083</v>
       </c>
       <c r="G9">
-        <v>0.1511494252873563</v>
+        <v>0.2018518518518518</v>
       </c>
       <c r="H9">
-        <v>0.1511494252873563</v>
+        <v>0.2018518518518518</v>
       </c>
       <c r="I9">
-        <v>0.1109195402298851</v>
+        <v>0.2860082304526749</v>
       </c>
       <c r="J9">
-        <v>0.08004316209242318</v>
+        <v>0.2584512330659938</v>
       </c>
       <c r="K9">
-        <v>1.77</v>
+        <v>1.1</v>
       </c>
       <c r="L9">
-        <v>0.1017241379310345</v>
+        <v>0.2263374485596708</v>
       </c>
       <c r="M9">
-        <v>0.529</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.03186746987951807</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.2988700564971751</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>0.529</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.03186746987951807</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.2988700564971751</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>6.84</v>
+        <v>5.77</v>
       </c>
       <c r="V9">
-        <v>0.4120481927710843</v>
+        <v>1.551075268817204</v>
       </c>
       <c r="W9">
-        <v>0.08349056603773586</v>
+        <v>0.06321839080459771</v>
       </c>
       <c r="X9">
-        <v>0.09329284571951575</v>
+        <v>0.1574845062704379</v>
       </c>
       <c r="Y9">
-        <v>-0.009802279681779894</v>
+        <v>-0.09426611546584018</v>
       </c>
       <c r="Z9">
-        <v>1.608876560332871</v>
+        <v>0.4200518582541055</v>
       </c>
       <c r="AA9">
-        <v>0.1287795673054243</v>
+        <v>0.1085629207174356</v>
       </c>
       <c r="AB9">
-        <v>0.09261611508979255</v>
+        <v>0.1574845062704379</v>
       </c>
       <c r="AC9">
-        <v>0.03616345221563171</v>
+        <v>-0.0489215855530023</v>
       </c>
       <c r="AD9">
-        <v>0.279</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.279</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>-6.561</v>
+        <v>-5.77</v>
       </c>
       <c r="AH9">
-        <v>0.01652941524971858</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>0.01305018943823378</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>-0.6535511505129992</v>
+        <v>2.814634146341464</v>
       </c>
       <c r="AK9">
-        <v>-0.4512690006190246</v>
+        <v>-0.4919011082693946</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AN9">
-        <v>0.1218340611353712</v>
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>53.46153846153846</v>
       </c>
       <c r="AP9">
-        <v>-2.865065502183406</v>
+        <v>-4.211678832116788</v>
+      </c>
+      <c r="AQ9">
+        <v>53.46153846153846</v>
       </c>
     </row>
     <row r="10">
@@ -1582,7 +1600,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prestige Assurance Plc (NGSE:PRESTIGE)</t>
+          <t>AXA Mansard Insurance Plc (NGSE:MANSARD)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1591,118 +1609,121 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.291</v>
+        <v>0.214</v>
       </c>
       <c r="E10">
-        <v>0.427</v>
+        <v>-0.106</v>
       </c>
       <c r="G10">
-        <v>0.1277027027027027</v>
+        <v>0.1103059581320451</v>
       </c>
       <c r="H10">
-        <v>0.1277027027027027</v>
+        <v>0.1103059581320451</v>
       </c>
       <c r="I10">
-        <v>0.1364864864864865</v>
+        <v>0.05821256038647343</v>
       </c>
       <c r="J10">
-        <v>0.1364864864864865</v>
+        <v>0.02910628019323672</v>
       </c>
       <c r="K10">
-        <v>2.11</v>
+        <v>2.54</v>
       </c>
       <c r="L10">
-        <v>0.1425675675675676</v>
+        <v>0.02045088566827697</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>5.21</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.1309045226130653</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>2.051181102362205</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>5.21</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.1309045226130653</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>2.051181102362205</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>10.7</v>
+        <v>40</v>
       </c>
       <c r="V10">
-        <v>0.6524390243902439</v>
+        <v>1.005025125628141</v>
       </c>
       <c r="W10">
-        <v>0.08791666666666666</v>
+        <v>0.03256410256410257</v>
       </c>
       <c r="X10">
-        <v>0.09315549302781131</v>
+        <v>0.1727226426282756</v>
       </c>
       <c r="Y10">
-        <v>-0.005238826361144658</v>
+        <v>-0.140158540064173</v>
       </c>
       <c r="Z10">
-        <v>0.7320209714116135</v>
+        <v>3.502439299512141</v>
       </c>
       <c r="AA10">
-        <v>0.09991097042239588</v>
+        <v>0.1019429796114041</v>
       </c>
       <c r="AB10">
-        <v>0.09261148688963715</v>
+        <v>0.1605474792068379</v>
       </c>
       <c r="AC10">
-        <v>0.007299483532758735</v>
+        <v>-0.05860449959543379</v>
       </c>
       <c r="AD10">
-        <v>0.234</v>
+        <v>7.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.234</v>
+        <v>7.3</v>
       </c>
       <c r="AG10">
-        <v>-10.466</v>
+        <v>-32.7</v>
       </c>
       <c r="AH10">
-        <v>0.01406757244198629</v>
+        <v>0.1549893842887474</v>
       </c>
       <c r="AI10">
-        <v>0.007327613202229599</v>
+        <v>0.08784596871239471</v>
       </c>
       <c r="AJ10">
-        <v>-1.763734411863836</v>
+        <v>-4.605633802816905</v>
       </c>
       <c r="AK10">
-        <v>-0.4928887633041348</v>
+        <v>-0.7587006960556846</v>
       </c>
       <c r="AL10">
-        <v>0.012</v>
+        <v>1.14</v>
       </c>
       <c r="AM10">
-        <v>0.012</v>
+        <v>1.14</v>
       </c>
       <c r="AN10">
-        <v>0.104</v>
+        <v>0.824858757062147</v>
       </c>
       <c r="AO10">
-        <v>168.3333333333333</v>
+        <v>6.342105263157896</v>
       </c>
       <c r="AP10">
-        <v>-4.651555555555555</v>
+        <v>-3.694915254237289</v>
       </c>
       <c r="AQ10">
-        <v>168.3333333333333</v>
+        <v>6.342105263157896</v>
       </c>
     </row>
     <row r="11">
@@ -1713,127 +1734,252 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Prestige Assurance Plc (NGSE:PRESTIGE)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.244</v>
+      </c>
+      <c r="E11">
+        <v>0.136</v>
+      </c>
+      <c r="G11">
+        <v>0.1011299435028249</v>
+      </c>
+      <c r="H11">
+        <v>0.1011299435028249</v>
+      </c>
+      <c r="I11">
+        <v>0.08418079096045199</v>
+      </c>
+      <c r="J11">
+        <v>0.07624101181304571</v>
+      </c>
+      <c r="K11">
+        <v>1.59</v>
+      </c>
+      <c r="L11">
+        <v>0.08983050847457628</v>
+      </c>
+      <c r="M11">
+        <v>0.767</v>
+      </c>
+      <c r="N11">
+        <v>0.06185483870967742</v>
+      </c>
+      <c r="O11">
+        <v>0.4823899371069182</v>
+      </c>
+      <c r="P11">
+        <v>0.767</v>
+      </c>
+      <c r="Q11">
+        <v>0.06185483870967742</v>
+      </c>
+      <c r="R11">
+        <v>0.4823899371069182</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>9.15</v>
+      </c>
+      <c r="V11">
+        <v>0.7379032258064516</v>
+      </c>
+      <c r="W11">
+        <v>0.05015772870662461</v>
+      </c>
+      <c r="X11">
+        <v>0.1604927756511475</v>
+      </c>
+      <c r="Y11">
+        <v>-0.1103350469445229</v>
+      </c>
+      <c r="Z11">
+        <v>0.8335688047471036</v>
+      </c>
+      <c r="AA11">
+        <v>0.06355212908971032</v>
+      </c>
+      <c r="AB11">
+        <v>0.1582680449644751</v>
+      </c>
+      <c r="AC11">
+        <v>-0.09471591587476476</v>
+      </c>
+      <c r="AD11">
+        <v>0.449</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0.449</v>
+      </c>
+      <c r="AG11">
+        <v>-8.701000000000001</v>
+      </c>
+      <c r="AH11">
+        <v>0.03494435364619815</v>
+      </c>
+      <c r="AI11">
+        <v>0.01392291233836708</v>
+      </c>
+      <c r="AJ11">
+        <v>-2.352257366855907</v>
+      </c>
+      <c r="AK11">
+        <v>-0.376682973288887</v>
+      </c>
+      <c r="AL11">
+        <v>0.003</v>
+      </c>
+      <c r="AM11">
+        <v>0.003</v>
+      </c>
+      <c r="AN11">
+        <v>0.2565714285714286</v>
+      </c>
+      <c r="AO11">
+        <v>496.6666666666666</v>
+      </c>
+      <c r="AP11">
+        <v>-4.972</v>
+      </c>
+      <c r="AQ11">
+        <v>496.6666666666666</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Linkage Assurance Plc (NGSE:LINKASSURE)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D11">
-        <v>0.129</v>
-      </c>
-      <c r="G11">
-        <v>0.3676923076923077</v>
-      </c>
-      <c r="H11">
-        <v>0.3676923076923077</v>
-      </c>
-      <c r="I11">
-        <v>-0.09333333333333334</v>
-      </c>
-      <c r="J11">
-        <v>-0.09333333333333334</v>
-      </c>
-      <c r="K11">
-        <v>-2.37</v>
-      </c>
-      <c r="L11">
-        <v>-0.1215384615384615</v>
-      </c>
-      <c r="M11">
-        <v>1.22</v>
-      </c>
-      <c r="N11">
-        <v>0.07052023121387282</v>
-      </c>
-      <c r="O11">
-        <v>-0.5147679324894514</v>
-      </c>
-      <c r="P11">
-        <v>1.22</v>
-      </c>
-      <c r="Q11">
-        <v>0.07052023121387282</v>
-      </c>
-      <c r="R11">
-        <v>-0.5147679324894514</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>7.63</v>
-      </c>
-      <c r="V11">
-        <v>0.4410404624277456</v>
-      </c>
-      <c r="W11">
-        <v>-0.0375</v>
-      </c>
-      <c r="X11">
-        <v>0.09238359951557647</v>
-      </c>
-      <c r="Y11">
-        <v>-0.1298835995155765</v>
-      </c>
-      <c r="Z11">
-        <v>0.3330259247873757</v>
-      </c>
-      <c r="AA11">
-        <v>-0.03108241964682174</v>
-      </c>
-      <c r="AB11">
-        <v>0.09238359951557647</v>
-      </c>
-      <c r="AC11">
-        <v>-0.1234660191623982</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>-7.63</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>-0.7890382626680453</v>
-      </c>
-      <c r="AK11">
-        <v>-0.1491108071135431</v>
-      </c>
-      <c r="AL11">
-        <v>0.023</v>
-      </c>
-      <c r="AM11">
-        <v>0.023</v>
-      </c>
-      <c r="AN11">
+      <c r="D12">
+        <v>0.123</v>
+      </c>
+      <c r="G12">
+        <v>-0.3632575757575758</v>
+      </c>
+      <c r="H12">
+        <v>-0.3632575757575758</v>
+      </c>
+      <c r="I12">
+        <v>-0.03143939393939394</v>
+      </c>
+      <c r="J12">
+        <v>-0.01571969696969697</v>
+      </c>
+      <c r="K12">
+        <v>-0.271</v>
+      </c>
+      <c r="L12">
+        <v>-0.01026515151515152</v>
+      </c>
+      <c r="M12">
         <v>-0</v>
       </c>
-      <c r="AO11">
-        <v>-79.1304347826087</v>
-      </c>
-      <c r="AP11">
-        <v>5.335664335664336</v>
-      </c>
-      <c r="AQ11">
-        <v>-79.1304347826087</v>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="V12">
+        <v>0.7240000000000001</v>
+      </c>
+      <c r="W12">
+        <v>-0.004608843537414966</v>
+      </c>
+      <c r="X12">
+        <v>0.1574845062704379</v>
+      </c>
+      <c r="Y12">
+        <v>-0.1620933498078529</v>
+      </c>
+      <c r="Z12">
+        <v>0.5159273011530193</v>
+      </c>
+      <c r="AA12">
+        <v>-0.008110220832519055</v>
+      </c>
+      <c r="AB12">
+        <v>0.1574845062704379</v>
+      </c>
+      <c r="AC12">
+        <v>-0.1655947271029569</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>-2.623188405797102</v>
+      </c>
+      <c r="AK12">
+        <v>-0.1680594243268338</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>-0</v>
+      </c>
+      <c r="AP12">
+        <v>26.00574712643678</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/nigeria/nigeria_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.133</v>
+        <v>0.1965</v>
       </c>
       <c r="E2">
-        <v>0.136</v>
+        <v>0.347</v>
       </c>
       <c r="G2">
-        <v>0.1275527629389614</v>
+        <v>0.2035530621785881</v>
       </c>
       <c r="H2">
-        <v>0.1275527629389614</v>
+        <v>0.2035530621785881</v>
       </c>
       <c r="I2">
-        <v>0.1446427007618881</v>
+        <v>0.1737961664329126</v>
       </c>
       <c r="J2">
-        <v>0.1142505635405622</v>
+        <v>0.1559653069483237</v>
       </c>
       <c r="K2">
-        <v>51.267</v>
+        <v>59.674</v>
       </c>
       <c r="L2">
-        <v>0.1122405639723268</v>
+        <v>0.1743630201028518</v>
       </c>
       <c r="M2">
-        <v>15.7</v>
+        <v>12.215</v>
       </c>
       <c r="N2">
-        <v>0.06821045314332884</v>
+        <v>0.05828323313293253</v>
       </c>
       <c r="O2">
-        <v>0.3062398814051924</v>
+        <v>0.2046955122834065</v>
       </c>
       <c r="P2">
-        <v>15.7</v>
+        <v>12.215</v>
       </c>
       <c r="Q2">
-        <v>0.06821045314332884</v>
+        <v>0.05828323313293253</v>
       </c>
       <c r="R2">
-        <v>0.3062398814051924</v>
+        <v>0.2046955122834065</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>171.03</v>
+        <v>107.92</v>
       </c>
       <c r="V2">
-        <v>0.7430594777772951</v>
+        <v>0.514934631167096</v>
       </c>
       <c r="W2">
-        <v>0.0776268945173431</v>
+        <v>0.09483778702150983</v>
       </c>
       <c r="X2">
-        <v>0.1590710607568138</v>
+        <v>0.1416441343307971</v>
       </c>
       <c r="Y2">
-        <v>-0.08144416623947072</v>
+        <v>-0.04680634730928726</v>
       </c>
       <c r="Z2">
-        <v>1.518786992086187</v>
+        <v>1.12904289993534</v>
       </c>
       <c r="AA2">
-        <v>0.1219508217690451</v>
+        <v>0.07995792146298009</v>
       </c>
       <c r="AB2">
-        <v>0.1578958424186642</v>
+        <v>0.1416101380614671</v>
       </c>
       <c r="AC2">
-        <v>-0.03681792659354859</v>
+        <v>-0.06571948412363865</v>
       </c>
       <c r="AD2">
-        <v>20.209</v>
+        <v>14.141</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>20.209</v>
+        <v>14.141</v>
       </c>
       <c r="AG2">
-        <v>-150.821</v>
+        <v>-93.779</v>
       </c>
       <c r="AH2">
-        <v>0.08071363812460311</v>
+        <v>0.06320819234671757</v>
       </c>
       <c r="AI2">
-        <v>0.03937004806071976</v>
+        <v>0.04269097122638803</v>
       </c>
       <c r="AJ2">
-        <v>-1.900729687834755</v>
+        <v>-0.8098289306655382</v>
       </c>
       <c r="AK2">
-        <v>-0.4406376085006676</v>
+        <v>-0.4199291602670595</v>
       </c>
       <c r="AL2">
-        <v>2.366</v>
+        <v>1.497</v>
       </c>
       <c r="AM2">
-        <v>2.366</v>
+        <v>1.497</v>
       </c>
       <c r="AN2">
-        <v>0.2813761800005569</v>
+        <v>0.2230160232147363</v>
       </c>
       <c r="AO2">
-        <v>27.92349957734573</v>
+        <v>39.73279893119572</v>
       </c>
       <c r="AP2">
-        <v>-2.099927598785887</v>
+        <v>-1.478977416098915</v>
       </c>
       <c r="AQ2">
-        <v>27.92349957734573</v>
+        <v>39.73279893119572</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Veritas Kapital Assurance Plc (NGSE:VERITASKAP)</t>
+          <t>AXA Mansard Insurance Plc (NGSE:MANSARD)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,41 +721,47 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.236</v>
+      </c>
+      <c r="E3">
+        <v>0.417</v>
+      </c>
       <c r="G3">
-        <v>0.09179104477611939</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="H3">
-        <v>0.09179104477611939</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="I3">
-        <v>0.0676865671641791</v>
+        <v>0.2193877551020408</v>
       </c>
       <c r="J3">
-        <v>0.0676865671641791</v>
+        <v>0.1869659193726752</v>
       </c>
       <c r="K3">
-        <v>1.43</v>
+        <v>17.2</v>
       </c>
       <c r="L3">
-        <v>0.1067164179104478</v>
+        <v>0.1755102040816326</v>
       </c>
       <c r="M3">
-        <v>0.001</v>
+        <v>4.15</v>
       </c>
       <c r="N3">
-        <v>0.0001615508885298869</v>
+        <v>0.07531760435571688</v>
       </c>
       <c r="O3">
-        <v>0.0006993006993006993</v>
+        <v>0.2412790697674419</v>
       </c>
       <c r="P3">
-        <v>0.001</v>
+        <v>4.15</v>
       </c>
       <c r="Q3">
-        <v>0.0001615508885298869</v>
+        <v>0.07531760435571688</v>
       </c>
       <c r="R3">
-        <v>0.0006993006993006993</v>
+        <v>0.2412790697674419</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,52 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>9.49</v>
+        <v>23.4</v>
       </c>
       <c r="V3">
-        <v>1.533117932148627</v>
+        <v>0.4246823956442831</v>
+      </c>
+      <c r="W3">
+        <v>0.2633996937212864</v>
       </c>
       <c r="X3">
-        <v>0.1574845062704379</v>
+        <v>0.1497016281645508</v>
+      </c>
+      <c r="Y3">
+        <v>0.1136980655567355</v>
+      </c>
+      <c r="Z3">
+        <v>3.008719145278153</v>
+      </c>
+      <c r="AA3">
+        <v>0.5625279411310994</v>
       </c>
       <c r="AB3">
-        <v>0.1574845062704379</v>
+        <v>0.1439364492032989</v>
+      </c>
+      <c r="AC3">
+        <v>0.4185914919278005</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>6.21</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>6.21</v>
       </c>
       <c r="AG3">
-        <v>-9.49</v>
+        <v>-17.19</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.1012885336812918</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.1038287911720448</v>
       </c>
       <c r="AJ3">
-        <v>2.875757575757576</v>
+        <v>-0.4534423634924821</v>
       </c>
       <c r="AK3">
-        <v>-0.5612063867534005</v>
+        <v>-0.4721230431200218</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.777</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.777</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.27117903930131</v>
+      </c>
+      <c r="AO3">
+        <v>27.67052767052767</v>
       </c>
       <c r="AP3">
-        <v>-6.683098591549296</v>
+        <v>-0.7506550218340611</v>
+      </c>
+      <c r="AQ3">
+        <v>27.67052767052767</v>
       </c>
     </row>
     <row r="4">
@@ -829,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.193</v>
+        <v>0.233</v>
       </c>
       <c r="E4">
-        <v>0.139</v>
+        <v>0.174</v>
       </c>
       <c r="G4">
-        <v>0.2038895859473024</v>
+        <v>0.2722513089005236</v>
       </c>
       <c r="H4">
-        <v>0.2038895859473024</v>
+        <v>0.2722513089005236</v>
       </c>
       <c r="I4">
-        <v>0.2151819322459222</v>
+        <v>0.2006980802792321</v>
       </c>
       <c r="J4">
-        <v>0.178772009273185</v>
+        <v>0.1689081171815675</v>
       </c>
       <c r="K4">
-        <v>25.1</v>
+        <v>21.4</v>
       </c>
       <c r="L4">
-        <v>0.157465495608532</v>
+        <v>0.1867364746945899</v>
       </c>
       <c r="M4">
-        <v>6.81</v>
+        <v>5.28</v>
       </c>
       <c r="N4">
-        <v>0.08719590268886043</v>
+        <v>0.08859060402684564</v>
       </c>
       <c r="O4">
-        <v>0.2713147410358566</v>
+        <v>0.2467289719626168</v>
       </c>
       <c r="P4">
-        <v>6.81</v>
+        <v>5.28</v>
       </c>
       <c r="Q4">
-        <v>0.08719590268886043</v>
+        <v>0.08859060402684564</v>
       </c>
       <c r="R4">
-        <v>0.2713147410358566</v>
+        <v>0.2467289719626168</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -877,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>47.2</v>
+        <v>29.5</v>
       </c>
       <c r="V4">
-        <v>0.6043533930857875</v>
+        <v>0.4949664429530201</v>
       </c>
       <c r="W4">
-        <v>0.2067545304777595</v>
+        <v>0.1592261904761905</v>
       </c>
       <c r="X4">
-        <v>0.1636755520904861</v>
+        <v>0.1449121076640604</v>
       </c>
       <c r="Y4">
-        <v>0.0430789783872734</v>
+        <v>0.01431408281213004</v>
       </c>
       <c r="Z4">
-        <v>1.681257251344795</v>
+        <v>1.231993119759192</v>
       </c>
       <c r="AA4">
-        <v>0.3005617369280212</v>
+        <v>0.2080936382391704</v>
       </c>
       <c r="AB4">
-        <v>0.1590395440547462</v>
+        <v>0.1426953228879282</v>
       </c>
       <c r="AC4">
-        <v>0.1415221928732751</v>
+        <v>0.06539831535124224</v>
       </c>
       <c r="AD4">
-        <v>5.82</v>
+        <v>2.75</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>5.82</v>
+        <v>2.75</v>
       </c>
       <c r="AG4">
-        <v>-41.38</v>
+        <v>-26.75</v>
       </c>
       <c r="AH4">
-        <v>0.06935176358436608</v>
+        <v>0.04410585404971933</v>
       </c>
       <c r="AI4">
-        <v>0.03596588802373007</v>
+        <v>0.02617801047120419</v>
       </c>
       <c r="AJ4">
-        <v>-1.126906318082789</v>
+        <v>-0.8143074581430746</v>
       </c>
       <c r="AK4">
-        <v>-0.3610190193683476</v>
+        <v>-0.3540701522170748</v>
       </c>
       <c r="AL4">
-        <v>0.6840000000000001</v>
+        <v>0.222</v>
       </c>
       <c r="AM4">
-        <v>0.6840000000000001</v>
+        <v>0.222</v>
       </c>
       <c r="AN4">
-        <v>0.164872521246459</v>
+        <v>0.1150627615062762</v>
       </c>
       <c r="AO4">
-        <v>50.14619883040935</v>
+        <v>103.6036036036036</v>
       </c>
       <c r="AP4">
-        <v>-1.172237960339944</v>
+        <v>-1.119246861924686</v>
       </c>
       <c r="AQ4">
-        <v>50.14619883040935</v>
+        <v>103.6036036036036</v>
       </c>
     </row>
     <row r="5">
@@ -963,40 +990,40 @@
         </is>
       </c>
       <c r="G5">
-        <v>0.1940035273368607</v>
+        <v>0.2714932126696832</v>
       </c>
       <c r="H5">
-        <v>0.1940035273368607</v>
+        <v>0.2714932126696832</v>
       </c>
       <c r="I5">
-        <v>0.2645502645502645</v>
+        <v>0.1794117647058823</v>
       </c>
       <c r="J5">
-        <v>0.2502986857825568</v>
+        <v>0.1783099311567037</v>
       </c>
       <c r="K5">
-        <v>14.6</v>
+        <v>8.57</v>
       </c>
       <c r="L5">
-        <v>0.2574955908289241</v>
+        <v>0.1938914027149321</v>
       </c>
       <c r="M5">
-        <v>2.31</v>
+        <v>1.79</v>
       </c>
       <c r="N5">
-        <v>0.04583333333333334</v>
+        <v>0.0502808988764045</v>
       </c>
       <c r="O5">
-        <v>0.1582191780821918</v>
+        <v>0.2088681446907818</v>
       </c>
       <c r="P5">
-        <v>2.31</v>
+        <v>1.79</v>
       </c>
       <c r="Q5">
-        <v>0.04583333333333334</v>
+        <v>0.0502808988764045</v>
       </c>
       <c r="R5">
-        <v>0.1582191780821918</v>
+        <v>0.2088681446907818</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1005,73 +1032,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="V5">
-        <v>0.376984126984127</v>
+        <v>0.5252808988764045</v>
       </c>
       <c r="W5">
-        <v>0.3022774327122154</v>
+        <v>0.1459965928449744</v>
       </c>
       <c r="X5">
-        <v>0.1576493458624802</v>
+        <v>0.1415920620362129</v>
       </c>
       <c r="Y5">
-        <v>0.1446280868497352</v>
+        <v>0.004404530808761492</v>
       </c>
       <c r="Z5">
-        <v>1.170858629661752</v>
+        <v>1.152662598445731</v>
       </c>
       <c r="AA5">
-        <v>0.2930643762415019</v>
+        <v>0.2055311885757655</v>
       </c>
       <c r="AB5">
-        <v>0.1575236398728533</v>
+        <v>0.1415920620362129</v>
       </c>
       <c r="AC5">
-        <v>0.1355407363686486</v>
+        <v>0.06393912653955253</v>
       </c>
       <c r="AD5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-18.9</v>
+        <v>-18.7</v>
       </c>
       <c r="AH5">
-        <v>0.00198019801980198</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.001677852348993289</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.6</v>
+        <v>-1.106508875739645</v>
       </c>
       <c r="AK5">
-        <v>-0.4655172413793103</v>
+        <v>-0.8947368421052631</v>
       </c>
       <c r="AL5">
-        <v>0.008999999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="AM5">
-        <v>0.008999999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="AN5">
-        <v>0.006410256410256411</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>1666.666666666667</v>
+        <v>74.11214953271028</v>
       </c>
       <c r="AP5">
-        <v>-1.211538461538461</v>
+        <v>-2.266666666666667</v>
       </c>
       <c r="AQ5">
-        <v>1666.666666666667</v>
+        <v>74.11214953271028</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1109,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sovereign Trust Insurance Plc (NGSE:SOVRENINS)</t>
+          <t>Consolidated Hallmark Holdings Plc (NGSE:CONHALLPLC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1091,118 +1118,115 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.103</v>
+        <v>0.166</v>
       </c>
       <c r="E6">
-        <v>0.106</v>
+        <v>0.277</v>
       </c>
       <c r="G6">
-        <v>0.1351851851851852</v>
+        <v>0.1381578947368421</v>
       </c>
       <c r="H6">
-        <v>0.1351851851851852</v>
+        <v>0.1381578947368421</v>
       </c>
       <c r="I6">
-        <v>0.1226851851851852</v>
+        <v>0.1618421052631579</v>
       </c>
       <c r="J6">
-        <v>0.1054484236302418</v>
+        <v>0.1111223571749888</v>
       </c>
       <c r="K6">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="L6">
-        <v>0.0962962962962963</v>
+        <v>0.1592105263157895</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>0.417</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.02329608938547486</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.1723140495867768</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>0.417</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.02329608938547486</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.1723140495867768</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>12.1</v>
+        <v>3.93</v>
       </c>
       <c r="V6">
-        <v>1.704225352112676</v>
+        <v>0.2195530726256983</v>
       </c>
       <c r="W6">
-        <v>0.09203539823008849</v>
+        <v>0.1105022831050228</v>
       </c>
       <c r="X6">
-        <v>0.2056938183949369</v>
+        <v>0.1505964169676533</v>
       </c>
       <c r="Y6">
-        <v>-0.1136584201648484</v>
+        <v>-0.04009413386263047</v>
       </c>
       <c r="Z6">
-        <v>1.484536082474227</v>
+        <v>1.059233449477352</v>
       </c>
       <c r="AA6">
-        <v>0.1565419897191218</v>
+        <v>0.1177045177045177</v>
       </c>
       <c r="AB6">
-        <v>0.1647413131497176</v>
+        <v>0.1443741478643967</v>
       </c>
       <c r="AC6">
-        <v>-0.00819932343059579</v>
+        <v>-0.02666963015987904</v>
       </c>
       <c r="AD6">
-        <v>4.12</v>
+        <v>2.24</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>4.12</v>
+        <v>2.24</v>
       </c>
       <c r="AG6">
-        <v>-7.98</v>
+        <v>-1.69</v>
       </c>
       <c r="AH6">
-        <v>0.3672014260249555</v>
+        <v>0.1112214498510427</v>
       </c>
       <c r="AI6">
-        <v>0.1480948957584472</v>
+        <v>0.1432225063938619</v>
       </c>
       <c r="AJ6">
-        <v>9.068181818181818</v>
+        <v>-0.1042566317088217</v>
       </c>
       <c r="AK6">
-        <v>-0.5076335877862596</v>
+        <v>-0.1443210930828352</v>
       </c>
       <c r="AL6">
-        <v>0.504</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>0.504</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>1.350819672131148</v>
-      </c>
-      <c r="AO6">
-        <v>5.257936507936508</v>
+        <v>0.8582375478927204</v>
       </c>
       <c r="AP6">
-        <v>-2.616393442622951</v>
-      </c>
-      <c r="AQ6">
-        <v>5.257936507936508</v>
+        <v>-0.6475095785440613</v>
       </c>
     </row>
     <row r="7">
@@ -1213,7 +1237,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Consolidated Hallmark Insurance Plc (NGSE:CHIPLC)</t>
+          <t>Sunu Assurances Nigeria Plc (NGSE:SUNUASSUR)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1222,46 +1246,43 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.143</v>
-      </c>
-      <c r="E7">
-        <v>0.349</v>
+        <v>0.229</v>
       </c>
       <c r="G7">
-        <v>0.1009615384615385</v>
+        <v>0.1219298245614035</v>
       </c>
       <c r="H7">
-        <v>0.1009615384615385</v>
+        <v>0.1219298245614035</v>
       </c>
       <c r="I7">
-        <v>0.1129807692307692</v>
+        <v>0.05894736842105263</v>
       </c>
       <c r="J7">
-        <v>0.09281804733727811</v>
+        <v>0.05470150901729848</v>
       </c>
       <c r="K7">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="L7">
-        <v>0.1028846153846154</v>
+        <v>0.2280701754385965</v>
       </c>
       <c r="M7">
-        <v>0.502</v>
+        <v>0.315</v>
       </c>
       <c r="N7">
-        <v>0.03098765432098766</v>
+        <v>0.04381084840055632</v>
       </c>
       <c r="O7">
-        <v>0.2345794392523364</v>
+        <v>0.1211538461538462</v>
       </c>
       <c r="P7">
-        <v>0.502</v>
+        <v>0.315</v>
       </c>
       <c r="Q7">
-        <v>0.03098765432098766</v>
+        <v>0.04381084840055632</v>
       </c>
       <c r="R7">
-        <v>0.2345794392523364</v>
+        <v>0.1211538461538462</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1270,67 +1291,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>9.970000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V7">
-        <v>0.6154320987654321</v>
+        <v>1.279554937413073</v>
       </c>
       <c r="W7">
-        <v>0.1014218009478673</v>
+        <v>0.1529411764705882</v>
       </c>
       <c r="X7">
-        <v>0.1698950960001985</v>
+        <v>0.1415920620362129</v>
       </c>
       <c r="Y7">
-        <v>-0.06847329505233121</v>
+        <v>0.01134911443437531</v>
       </c>
       <c r="Z7">
-        <v>1.430634844212119</v>
+        <v>1.480519480519481</v>
       </c>
       <c r="AA7">
-        <v>0.13278873269244</v>
+        <v>0.08098664971392244</v>
       </c>
       <c r="AB7">
-        <v>0.1600529904547495</v>
+        <v>0.1415920620362129</v>
       </c>
       <c r="AC7">
-        <v>-0.02726425776230956</v>
+        <v>-0.0606054123222905</v>
       </c>
       <c r="AD7">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>-7.550000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.129967776584318</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.09950657894736842</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.8728323699421967</v>
+        <v>4.577114427860699</v>
       </c>
       <c r="AK7">
-        <v>-0.5261324041811848</v>
+        <v>-3.285714285714285</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AN7">
-        <v>0.8768115942028986</v>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>224</v>
       </c>
       <c r="AP7">
-        <v>-2.735507246376812</v>
+        <v>-9.25553319919517</v>
+      </c>
+      <c r="AQ7">
+        <v>224</v>
       </c>
     </row>
     <row r="8">
@@ -1341,7 +1368,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sunu Assurances Nigeria Plc (NGSE:SUNUASSUR)</t>
+          <t>Sovereign Trust Insurance Plc (NGSE:SOVRENINS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1350,115 +1377,118 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.07440000000000001</v>
+        <v>0.203</v>
       </c>
       <c r="E8">
-        <v>0.375</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="G8">
-        <v>0.1393162393162393</v>
+        <v>0.1432748538011696</v>
       </c>
       <c r="H8">
-        <v>0.1393162393162393</v>
+        <v>0.1432748538011696</v>
       </c>
       <c r="I8">
-        <v>0.1350427350427351</v>
+        <v>0.08362573099415203</v>
       </c>
       <c r="J8">
-        <v>0.0852815332815333</v>
+        <v>0.07255946884755748</v>
       </c>
       <c r="K8">
-        <v>0.958</v>
+        <v>1.16</v>
       </c>
       <c r="L8">
-        <v>0.08188034188034188</v>
+        <v>0.06783625730994151</v>
       </c>
       <c r="M8">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.02659574468085107</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.104384133611691</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.02659574468085107</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.104384133611691</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>9.300000000000001</v>
+        <v>7.51</v>
       </c>
       <c r="V8">
-        <v>2.473404255319149</v>
+        <v>1.398510242085661</v>
       </c>
       <c r="W8">
-        <v>0.05537572254335259</v>
+        <v>0.04894514767932489</v>
       </c>
       <c r="X8">
-        <v>0.1574845062704379</v>
+        <v>0.1808521214843084</v>
       </c>
       <c r="Y8">
-        <v>-0.1021087837270853</v>
+        <v>-0.1319069738049835</v>
       </c>
       <c r="Z8">
-        <v>1.302895322939866</v>
+        <v>1.087786259541985</v>
       </c>
       <c r="AA8">
-        <v>0.1111129108456503</v>
+        <v>0.07892919321203772</v>
       </c>
       <c r="AB8">
-        <v>0.1574845062704379</v>
+        <v>0.1497627491370245</v>
       </c>
       <c r="AC8">
-        <v>-0.04637159542478761</v>
+        <v>-0.07083355592498682</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AG8">
-        <v>-9.300000000000001</v>
+        <v>-4.58</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.3530120481927711</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.1700522344747533</v>
       </c>
       <c r="AJ8">
-        <v>1.67870036101083</v>
+        <v>-5.79746835443038</v>
       </c>
       <c r="AK8">
-        <v>-1.120481927710843</v>
+        <v>-0.47119341563786</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>0.376</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>0.376</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1.902597402597403</v>
+      </c>
+      <c r="AO8">
+        <v>3.803191489361702</v>
       </c>
       <c r="AP8">
-        <v>-4.492753623188406</v>
+        <v>-2.974025974025974</v>
+      </c>
+      <c r="AQ8">
+        <v>3.803191489361702</v>
       </c>
     </row>
     <row r="9">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Regency Alliance Insurance Plc (NGSE:REGALINS)</t>
+          <t>Linkage Assurance Plc (NGSE:LINKASSURE)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1478,28 +1508,28 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.182</v>
+        <v>0.167</v>
       </c>
       <c r="E9">
-        <v>-0.0083</v>
+        <v>1.004</v>
       </c>
       <c r="G9">
-        <v>0.2018518518518518</v>
+        <v>0.3542168674698795</v>
       </c>
       <c r="H9">
-        <v>0.2018518518518518</v>
+        <v>0.3542168674698795</v>
       </c>
       <c r="I9">
-        <v>0.2860082304526749</v>
+        <v>0.1849397590361445</v>
       </c>
       <c r="J9">
-        <v>0.2584512330659938</v>
+        <v>0.1727261014037387</v>
       </c>
       <c r="K9">
-        <v>1.1</v>
+        <v>4.98</v>
       </c>
       <c r="L9">
-        <v>0.2263374485596708</v>
+        <v>0.3</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1523,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>5.77</v>
+        <v>4.52</v>
       </c>
       <c r="V9">
-        <v>1.551075268817204</v>
+        <v>0.3587301587301587</v>
       </c>
       <c r="W9">
-        <v>0.06321839080459771</v>
+        <v>0.07917329093799683</v>
       </c>
       <c r="X9">
-        <v>0.1574845062704379</v>
+        <v>0.1415920620362129</v>
       </c>
       <c r="Y9">
-        <v>-0.09426611546584018</v>
+        <v>-0.06241877109821611</v>
       </c>
       <c r="Z9">
-        <v>0.4200518582541055</v>
+        <v>0.3082636954503251</v>
       </c>
       <c r="AA9">
-        <v>0.1085629207174356</v>
+        <v>0.05324518631944408</v>
       </c>
       <c r="AB9">
-        <v>0.1574845062704379</v>
+        <v>0.1415920620362129</v>
       </c>
       <c r="AC9">
-        <v>-0.0489215855530023</v>
+        <v>-0.08834687571676886</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -1559,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>-5.77</v>
+        <v>-4.52</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -1568,28 +1598,22 @@
         <v>0</v>
       </c>
       <c r="AJ9">
-        <v>2.814634146341464</v>
+        <v>-0.5594059405940593</v>
       </c>
       <c r="AK9">
-        <v>-0.4919011082693946</v>
+        <v>-0.1426767676767677</v>
       </c>
       <c r="AL9">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AN9">
         <v>0</v>
       </c>
-      <c r="AO9">
-        <v>53.46153846153846</v>
-      </c>
       <c r="AP9">
-        <v>-4.211678832116788</v>
-      </c>
-      <c r="AQ9">
-        <v>53.46153846153846</v>
+        <v>-1.341246290801187</v>
       </c>
     </row>
     <row r="10">
@@ -1600,7 +1624,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AXA Mansard Insurance Plc (NGSE:MANSARD)</t>
+          <t>Regency Alliance Insurance Plc (NGSE:REGALINS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1609,121 +1633,118 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.214</v>
+        <v>0.0143</v>
       </c>
       <c r="E10">
-        <v>-0.106</v>
+        <v>0.129</v>
       </c>
       <c r="G10">
-        <v>0.1103059581320451</v>
+        <v>0.1963470319634703</v>
       </c>
       <c r="H10">
-        <v>0.1103059581320451</v>
+        <v>0.1963470319634703</v>
       </c>
       <c r="I10">
-        <v>0.05821256038647343</v>
+        <v>0.08234398782343988</v>
       </c>
       <c r="J10">
-        <v>0.02910628019323672</v>
+        <v>0.07652311971867948</v>
       </c>
       <c r="K10">
-        <v>2.54</v>
+        <v>0.538</v>
       </c>
       <c r="L10">
-        <v>0.02045088566827697</v>
+        <v>0.08188736681887367</v>
       </c>
       <c r="M10">
-        <v>5.21</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.1309045226130653</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>2.051181102362205</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>5.21</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.1309045226130653</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>2.051181102362205</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>40</v>
+        <v>2.22</v>
       </c>
       <c r="V10">
-        <v>1.005025125628141</v>
+        <v>0.7789473684210527</v>
       </c>
       <c r="W10">
-        <v>0.03256410256410257</v>
+        <v>0.03091954022988506</v>
       </c>
       <c r="X10">
-        <v>0.1727226426282756</v>
+        <v>0.1415920620362129</v>
       </c>
       <c r="Y10">
-        <v>-0.140158540064173</v>
+        <v>-0.1106725218063279</v>
       </c>
       <c r="Z10">
-        <v>3.502439299512141</v>
+        <v>0.5649183147033535</v>
       </c>
       <c r="AA10">
-        <v>0.1019429796114041</v>
+        <v>0.04322931182731937</v>
       </c>
       <c r="AB10">
-        <v>0.1605474792068379</v>
+        <v>0.1415920620362129</v>
       </c>
       <c r="AC10">
-        <v>-0.05860449959543379</v>
+        <v>-0.09836275020889357</v>
       </c>
       <c r="AD10">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>-32.7</v>
+        <v>-2.22</v>
       </c>
       <c r="AH10">
-        <v>0.1549893842887474</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>0.08784596871239471</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>-4.605633802816905</v>
+        <v>-3.523809523809525</v>
       </c>
       <c r="AK10">
-        <v>-0.7587006960556846</v>
+        <v>-0.2617924528301888</v>
       </c>
       <c r="AL10">
-        <v>1.14</v>
+        <v>0.011</v>
       </c>
       <c r="AM10">
-        <v>1.14</v>
+        <v>0.011</v>
       </c>
       <c r="AN10">
-        <v>0.824858757062147</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>6.342105263157896</v>
+        <v>49.18181818181819</v>
       </c>
       <c r="AP10">
-        <v>-3.694915254237289</v>
+        <v>-3.94316163410302</v>
       </c>
       <c r="AQ10">
-        <v>6.342105263157896</v>
+        <v>49.18181818181819</v>
       </c>
     </row>
     <row r="11">
@@ -1734,7 +1755,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prestige Assurance Plc (NGSE:PRESTIGE)</t>
+          <t>Veritas Kapital Assurance Plc (NGSE:VERITASKAP)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1742,47 +1763,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D11">
-        <v>0.244</v>
-      </c>
-      <c r="E11">
-        <v>0.136</v>
-      </c>
       <c r="G11">
-        <v>0.1011299435028249</v>
+        <v>0.2368082368082368</v>
       </c>
       <c r="H11">
-        <v>0.1011299435028249</v>
+        <v>0.2368082368082368</v>
       </c>
       <c r="I11">
-        <v>0.08418079096045199</v>
+        <v>0.006048906048906049</v>
       </c>
       <c r="J11">
-        <v>0.07624101181304571</v>
+        <v>0.005691038832400089</v>
       </c>
       <c r="K11">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="L11">
-        <v>0.08983050847457628</v>
+        <v>0.1814671814671815</v>
       </c>
       <c r="M11">
-        <v>0.767</v>
+        <v>0.008</v>
       </c>
       <c r="N11">
-        <v>0.06185483870967742</v>
+        <v>0.001386481802426343</v>
       </c>
       <c r="O11">
-        <v>0.4823899371069182</v>
+        <v>0.005673758865248227</v>
       </c>
       <c r="P11">
-        <v>0.767</v>
+        <v>0.008</v>
       </c>
       <c r="Q11">
-        <v>0.06185483870967742</v>
+        <v>0.001386481802426343</v>
       </c>
       <c r="R11">
-        <v>0.4823899371069182</v>
+        <v>0.005673758865248227</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1791,73 +1806,67 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>9.15</v>
+        <v>6.58</v>
       </c>
       <c r="V11">
-        <v>0.7379032258064516</v>
+        <v>1.140381282495667</v>
       </c>
       <c r="W11">
-        <v>0.05015772870662461</v>
+        <v>0.05826446280991735</v>
       </c>
       <c r="X11">
-        <v>0.1604927756511475</v>
+        <v>0.1415920620362129</v>
       </c>
       <c r="Y11">
-        <v>-0.1103350469445229</v>
+        <v>-0.0833275992262956</v>
       </c>
       <c r="Z11">
-        <v>0.8335688047471036</v>
+        <v>0.6052816078523019</v>
       </c>
       <c r="AA11">
-        <v>0.06355212908971032</v>
+        <v>0.003444681134825013</v>
       </c>
       <c r="AB11">
-        <v>0.1582680449644751</v>
+        <v>0.1415920620362129</v>
       </c>
       <c r="AC11">
-        <v>-0.09471591587476476</v>
+        <v>-0.1381473809013879</v>
       </c>
       <c r="AD11">
-        <v>0.449</v>
+        <v>0</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.449</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>-8.701000000000001</v>
+        <v>-6.58</v>
       </c>
       <c r="AH11">
-        <v>0.03494435364619815</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>0.01392291233836708</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>-2.352257366855907</v>
+        <v>8.123456790123452</v>
       </c>
       <c r="AK11">
-        <v>-0.376682973288887</v>
+        <v>-0.5970961887477313</v>
       </c>
       <c r="AL11">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>0.2565714285714286</v>
-      </c>
-      <c r="AO11">
-        <v>496.6666666666666</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>-4.972</v>
-      </c>
-      <c r="AQ11">
-        <v>496.6666666666666</v>
+        <v>-21.86046511627907</v>
       </c>
     </row>
     <row r="12">
@@ -1868,7 +1877,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Linkage Assurance Plc (NGSE:LINKASSURE)</t>
+          <t>Prestige Assurance Plc (NGSE:PRESTIGE)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1877,109 +1886,118 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.123</v>
+        <v>0.19</v>
       </c>
       <c r="G12">
-        <v>-0.3632575757575758</v>
+        <v>0.02907407407407407</v>
       </c>
       <c r="H12">
-        <v>-0.3632575757575758</v>
+        <v>0.02907407407407407</v>
       </c>
       <c r="I12">
-        <v>-0.03143939393939394</v>
+        <v>-0.1083333333333333</v>
       </c>
       <c r="J12">
-        <v>-0.01571969696969697</v>
+        <v>-0.1083333333333333</v>
       </c>
       <c r="K12">
-        <v>-0.271</v>
+        <v>-0.604</v>
       </c>
       <c r="L12">
-        <v>-0.01026515151515152</v>
+        <v>-0.05592592592592592</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>0.255</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.03355263157894737</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>-0.4221854304635762</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>0.255</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.03355263157894737</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>-0.4221854304635762</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>9.050000000000001</v>
+        <v>2.36</v>
       </c>
       <c r="V12">
-        <v>0.7240000000000001</v>
+        <v>0.3105263157894737</v>
       </c>
       <c r="W12">
-        <v>-0.004608843537414966</v>
+        <v>-0.0189937106918239</v>
       </c>
       <c r="X12">
-        <v>0.1574845062704379</v>
+        <v>0.1416962066253812</v>
       </c>
       <c r="Y12">
-        <v>-0.1620933498078529</v>
+        <v>-0.1606899173172051</v>
       </c>
       <c r="Z12">
-        <v>0.5159273011530193</v>
+        <v>0.4675527079094333</v>
       </c>
       <c r="AA12">
-        <v>-0.008110220832519055</v>
+        <v>-0.05065154335685526</v>
       </c>
       <c r="AB12">
-        <v>0.1574845062704379</v>
+        <v>0.1416282140867211</v>
       </c>
       <c r="AC12">
-        <v>-0.1655947271029569</v>
+        <v>-0.1922797574435764</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="AG12">
-        <v>-9.050000000000001</v>
+        <v>-2.349</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.001445276573380633</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>0.0006317845040491643</v>
       </c>
       <c r="AJ12">
-        <v>-2.623188405797102</v>
+        <v>-0.4473433631689202</v>
       </c>
       <c r="AK12">
-        <v>-0.1680594243268338</v>
+        <v>-0.1560693641618497</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AN12">
-        <v>-0</v>
+        <v>-0.0107843137254902</v>
+      </c>
+      <c r="AO12">
+        <v>-1170</v>
       </c>
       <c r="AP12">
-        <v>26.00574712643678</v>
+        <v>2.302941176470588</v>
+      </c>
+      <c r="AQ12">
+        <v>-1170</v>
       </c>
     </row>
   </sheetData>
